--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486979_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486979_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9825</v>
+        <v>5.9745</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3364</v>
+        <v>4.5655</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6461</v>
+        <v>1.409</v>
       </c>
       <c r="G2" t="n">
         <v>4.1501</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9457</v>
+        <v>0.9377</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5224</v>
+        <v>0.7514</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4234</v>
+        <v>0.1862</v>
       </c>
       <c r="V2" t="n">
         <v>0.0653</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5221</v>
+        <v>3.3787</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8634</v>
+        <v>2.72</v>
       </c>
       <c r="F3" t="n">
         <v>0.6587</v>
@@ -688,10 +688,10 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1739</v>
+        <v>1.0306</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0227</v>
+        <v>0.8793</v>
       </c>
       <c r="U3" t="n">
         <v>0.1513</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.834</v>
+        <v>1.0184</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9454</v>
+        <v>1.0113</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1114</v>
+        <v>0.0072</v>
       </c>
       <c r="G4" t="n">
         <v>-1.7371</v>
@@ -766,13 +766,13 @@
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3657</v>
+        <v>0.5502</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5152</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1495</v>
+        <v>-0.0309</v>
       </c>
       <c r="V4" t="n">
         <v>1.1786</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6128</v>
+        <v>0.724</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4476</v>
+        <v>2.6181</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8348</v>
+        <v>-1.894</v>
       </c>
       <c r="G5" t="n">
         <v>2.5485</v>
@@ -844,13 +844,13 @@
         <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1944</v>
+        <v>-0.0833</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2558</v>
+        <v>-0.0853</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0613</v>
+        <v>0.002</v>
       </c>
       <c r="V5" t="n">
         <v>-2.3573</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.1932</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3408</v>
+        <v>-0.0331</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2625</v>
+        <v>0.2263</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.924</v>
+        <v>3.7849</v>
       </c>
       <c r="H6" t="n">
-        <v>1.836</v>
+        <v>2.9162</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.76</v>
+        <v>0.8686</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.3722</v>
+        <v>3.5918</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6935</v>
+        <v>1.658</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.0657</v>
+        <v>1.9338</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5518</v>
+        <v>0.193</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1425</v>
+        <v>1.2582</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6943</v>
+        <v>-1.0652</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4374</v>
+        <v>-4.9282</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-6.1603</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2732</v>
+        <v>0.158</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3875</v>
+        <v>0.1781</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6607</v>
+        <v>-0.0201</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1351</v>
+        <v>1.1786</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4189</v>
+        <v>2.3573</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2838</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4392</v>
+        <v>0.1919</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5174</v>
+        <v>-0.9224</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0781</v>
+        <v>1.1143</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7849</v>
+        <v>-2.924</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9162</v>
+        <v>1.836</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8686</v>
+        <v>-4.76</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5918</v>
+        <v>-2.3722</v>
       </c>
       <c r="K7" t="n">
-        <v>1.658</v>
+        <v>1.6935</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9338</v>
+        <v>-4.0657</v>
       </c>
       <c r="M7" t="n">
-        <v>0.193</v>
+        <v>-0.5518</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2582</v>
+        <v>0.1425</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0652</v>
+        <v>-0.6943</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.9282</v>
+        <v>1.4374</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.1603</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4745</v>
+        <v>0.5434</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3062</v>
+        <v>0.0309</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1683</v>
+        <v>0.5125</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1786</v>
+        <v>1.1351</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3573</v>
+        <v>1.4189</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1786</v>
+        <v>-0.2838</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9157</v>
+        <v>-0.8499</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6706</v>
+        <v>-1.6048</v>
       </c>
       <c r="F8" t="n">
         <v>0.7549</v>
@@ -1078,10 +1078,10 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.5152</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4534</v>
+        <v>-0.3875</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9006</v>
+        <v>-1.6411</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4645</v>
+        <v>-1.294</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4361</v>
+        <v>-0.3472</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0727</v>
@@ -1156,13 +1156,13 @@
         <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.793</v>
+        <v>-0.5336</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4457</v>
+        <v>-0.2752</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3473</v>
+        <v>-0.2584</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8295</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0298</v>
+        <v>-2.352</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1893</v>
+        <v>-2.6004</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1595</v>
+        <v>0.2485</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5922</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9752</v>
+        <v>-0.2973</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7169</v>
+        <v>-0.128</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2583</v>
+        <v>-0.1694</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8731</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.8026</v>
+        <v>-8.1938</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.0168</v>
+        <v>-7.408</v>
       </c>
       <c r="F11" t="n">
         <v>-0.7858000000000001</v>
@@ -1312,10 +1312,10 @@
         <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.4378</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9568</v>
+        <v>0.5655</v>
       </c>
       <c r="U11" t="n">
         <v>-0.1277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2148</v>
+        <v>-1.556100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.606599999999999</v>
+        <v>-2.9478</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3917</v>
+        <v>1.3919</v>
       </c>
       <c r="G12" t="n">
         <v>-0.02640000000000065</v>
@@ -1390,13 +1390,13 @@
         <v>12.3206</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5694</v>
+        <v>2.2283</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4516</v>
+        <v>2.1103</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1179</v>
+        <v>0.1178</v>
       </c>
       <c r="V12" t="n">
         <v>0.3490000000000002</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.846</v>
+        <v>9.994899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>7.142</v>
+        <v>7.665</v>
       </c>
       <c r="F13" t="n">
-        <v>1.704</v>
+        <v>2.3299</v>
       </c>
       <c r="G13" t="n">
         <v>6.5622</v>
@@ -1468,13 +1468,13 @@
         <v>2.0534</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8415</v>
+        <v>-0.6926</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0462</v>
+        <v>-0.5232</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7953</v>
+        <v>-0.1694</v>
       </c>
       <c r="V13" t="n">
         <v>4.1252</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7886</v>
+        <v>2.0518</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2102</v>
+        <v>-1.3149</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9988</v>
+        <v>3.3667</v>
       </c>
       <c r="G14" t="n">
         <v>1.9192</v>
@@ -1546,13 +1546,13 @@
         <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5413</v>
+        <v>-0.278</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2094</v>
+        <v>-0.314</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3319</v>
+        <v>0.036</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>I. CORRALIZA COBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0178</v>
+        <v>1.3318</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0443</v>
+        <v>-0.8815</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0265</v>
+        <v>2.2132</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4114</v>
+        <v>0.3181</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.2008</v>
+        <v>-1.8548</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7894</v>
+        <v>2.1729</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4127</v>
+        <v>-0.2696</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.202</v>
+        <v>-1.1635</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7893</v>
+        <v>0.8939</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9987</v>
+        <v>0.5876</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9988</v>
+        <v>-0.6913</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>1.279</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6427</v>
+        <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5462</v>
+        <v>0.1656</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0381</v>
+        <v>-0.1745</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5081</v>
+        <v>0.3401</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2402</v>
+        <v>-0.5893</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4189</v>
+        <v>0.5893</v>
       </c>
       <c r="X15" t="n">
         <v>-1.1786</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. CORRALIZA COBA</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5281</v>
+        <v>0.2628</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6137</v>
+        <v>0.4167</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1418</v>
+        <v>-0.1538</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3181</v>
+        <v>-2.4114</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8548</v>
+        <v>-4.2008</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1729</v>
+        <v>1.7894</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2696</v>
+        <v>-1.4127</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1635</v>
+        <v>-2.202</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8939</v>
+        <v>0.7893</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5876</v>
+        <v>-0.9987</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6913</v>
+        <v>-1.9988</v>
       </c>
       <c r="O16" t="n">
-        <v>1.279</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4641</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6381</v>
+        <v>0.7913</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9068000000000001</v>
+        <v>0.4105</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2687</v>
+        <v>0.3808</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5893</v>
+        <v>0.2402</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5893</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
         <v>-1.1786</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>P. SUÁREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4959</v>
+        <v>-0.4177</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0868</v>
+        <v>-1.991</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5826</v>
+        <v>1.5733</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9022</v>
+        <v>-2.3471</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.545</v>
+        <v>-1.7551</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4472</v>
+        <v>-0.592</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4434</v>
+        <v>-1.7585</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5095</v>
+        <v>-0.5611</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9338</v>
+        <v>-1.1974</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5412</v>
+        <v>-0.5887</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0546</v>
+        <v>-1.194</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4866</v>
+        <v>0.6054</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1913</v>
+        <v>0.0813</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6701</v>
+        <v>-0.2326</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4788</v>
+        <v>0.3139</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0942</v>
+        <v>-0.6214</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4095</v>
+        <v>1.5637</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3153</v>
+        <v>-2.1851</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3471</v>
+        <v>0.9022</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7551</v>
+        <v>-0.545</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.592</v>
+        <v>1.4472</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.7585</v>
+        <v>2.4434</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5611</v>
+        <v>0.5095</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1974</v>
+        <v>1.9338</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5887</v>
+        <v>-1.5412</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.194</v>
+        <v>-1.0546</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6054</v>
+        <v>-0.4866</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8481</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5951</v>
+        <v>0.0658</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.651</v>
+        <v>0.1471</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0559</v>
+        <v>-0.0813</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2145</v>
+        <v>-1.1901</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2331</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4477</v>
+        <v>-1.1094</v>
       </c>
       <c r="G20" t="n">
         <v>0.2118</v>
@@ -2014,13 +2014,13 @@
         <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3416</v>
+        <v>0.3661</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6778</v>
+        <v>0.364</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3362</v>
+        <v>0.002</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7679</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9918</v>
+        <v>-1.2685</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.538</v>
+        <v>-0.2766</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5462</v>
+        <v>-0.992</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5349</v>
+        <v>-3.1968</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7583</v>
+        <v>-1.2944</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2234</v>
+        <v>-1.9024</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5149</v>
+        <v>-1.2924</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0409</v>
+        <v>-0.016</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.474</v>
+        <v>-1.2763</v>
       </c>
       <c r="M21" t="n">
-        <v>0.98</v>
+        <v>-1.9044</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7174</v>
+        <v>-1.2783</v>
       </c>
       <c r="O21" t="n">
-        <v>1.6974</v>
+        <v>-0.6261</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9887</v>
+        <v>0.1336</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8168</v>
+        <v>-0.1628</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1719</v>
+        <v>0.2964</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4189</v>
+        <v>1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.074</v>
+        <v>-2.1011</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9042</v>
+        <v>-1.8434</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1698</v>
+        <v>-0.2577</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1968</v>
+        <v>-0.381</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2944</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9024</v>
+        <v>0.3816</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2924</v>
+        <v>0.2682</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.016</v>
+        <v>0.0973</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2763</v>
+        <v>0.1709</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9044</v>
+        <v>-0.6492</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2783</v>
+        <v>-0.8599</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6261</v>
+        <v>0.2107</v>
       </c>
       <c r="P22" t="n">
-        <v>0.616</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.371</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7905</v>
+        <v>-0.2985</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1186</v>
+        <v>-0.0726</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1786</v>
+        <v>-0.9384</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1454</v>
+        <v>-3.0885</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2618</v>
+        <v>-4.6887</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8836000000000001</v>
+        <v>1.6002</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.381</v>
+        <v>-1.5349</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-1.7583</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3816</v>
+        <v>0.2234</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2682</v>
+        <v>-2.5149</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0973</v>
+        <v>-1.0409</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1709</v>
+        <v>-1.474</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6492</v>
+        <v>0.98</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8599</v>
+        <v>-0.7174</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2107</v>
+        <v>1.6974</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6427</v>
+        <v>2.0534</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4154</v>
+        <v>0.892</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7169</v>
+        <v>0.6662</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6985</v>
+        <v>0.2259</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9384</v>
+        <v>-1.4189</v>
       </c>
       <c r="W23" t="n">
         <v>0.2402</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1786</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.214900000000001</v>
+        <v>5.004199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.391699999999999</v>
+        <v>-1.3919</v>
       </c>
       <c r="F24" t="n">
-        <v>3.6066</v>
+        <v>6.396000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.0266000000000004</v>
@@ -2302,13 +2302,13 @@
         <v>3.254</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.1104</v>
+        <v>-3.110399999999999</v>
       </c>
       <c r="L24" t="n">
         <v>6.364399999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2276</v>
+        <v>-3.227599999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-9.9788</v>
@@ -2326,16 +2326,16 @@
         <v>16.4272</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5696</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1180000000000002</v>
+        <v>-0.1178</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4516</v>
+        <v>1.3377</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3490999999999999</v>
+        <v>-0.3490999999999997</v>
       </c>
       <c r="W24" t="n">
         <v>7.7924</v>
